--- a/output_data/charts/crashSeverityByType-Knox.xlsx
+++ b/output_data/charts/crashSeverityByType-Knox.xlsx
@@ -37,43 +37,43 @@
     <t>Head On</t>
   </si>
   <si>
+    <t>Sideswipe - Passing</t>
+  </si>
+  <si>
+    <t>Rear End</t>
+  </si>
+  <si>
     <t>Animal</t>
   </si>
   <si>
+    <t>Pedestrian</t>
+  </si>
+  <si>
+    <t>Pedalcycles</t>
+  </si>
+  <si>
+    <t>Sideswipe - Meeting</t>
+  </si>
+  <si>
+    <t>Right Turn</t>
+  </si>
+  <si>
     <t>Overturning</t>
   </si>
   <si>
-    <t>Sideswipe - Passing</t>
-  </si>
-  <si>
-    <t>Pedestrian</t>
+    <t>Parked Vehicle</t>
+  </si>
+  <si>
+    <t>Other Object</t>
+  </si>
+  <si>
+    <t>Other Non-Collision</t>
+  </si>
+  <si>
+    <t>Left Turn</t>
   </si>
   <si>
     <t>Backing</t>
-  </si>
-  <si>
-    <t>Left Turn</t>
-  </si>
-  <si>
-    <t>Other Object</t>
-  </si>
-  <si>
-    <t>Other Non-Collision</t>
-  </si>
-  <si>
-    <t>Pedalcycles</t>
-  </si>
-  <si>
-    <t>Parked Vehicle</t>
-  </si>
-  <si>
-    <t>Rear End</t>
-  </si>
-  <si>
-    <t>Right Turn</t>
-  </si>
-  <si>
-    <t>Sideswipe - Meeting</t>
   </si>
   <si>
     <t>Unknown</t>
@@ -222,43 +222,43 @@
                   <c:v>Head On</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Rear End</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Overturning</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>Pedalcycles</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Right Turn</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Overturning</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Other Non-Collision</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Left Turn</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Other Non-Collision</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Pedalcycles</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Right Turn</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Unknown</c:v>
@@ -273,25 +273,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>39.39393939393939</c:v>
+                  <c:v>34.48275862068966</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24.24242424242424</c:v>
+                  <c:v>27.58620689655172</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24.24242424242424</c:v>
+                  <c:v>24.13793103448276</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.03030303030303</c:v>
+                  <c:v>3.448275862068965</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.03030303030303</c:v>
+                  <c:v>3.448275862068965</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.03030303030303</c:v>
+                  <c:v>3.448275862068965</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.03030303030303</c:v>
+                  <c:v>3.448275862068965</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -364,43 +364,43 @@
                   <c:v>Head On</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Rear End</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Overturning</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>Pedalcycles</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Right Turn</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Overturning</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Other Non-Collision</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Left Turn</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Other Non-Collision</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Pedalcycles</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Right Turn</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Unknown</c:v>
@@ -415,49 +415,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>42.95302013422819</c:v>
+                  <c:v>39.31034482758621</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.12080536912752</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.711409395973154</c:v>
+                  <c:v>4.137931034482759</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.697986577181208</c:v>
+                  <c:v>5.517241379310345</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.711409395973154</c:v>
+                  <c:v>5.517241379310345</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.026845637583892</c:v>
+                  <c:v>5.517241379310345</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.684563758389262</c:v>
+                  <c:v>3.448275862068965</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.6896551724137931</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.369127516778524</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1.379310344827586</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>7.586206896551724</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.342281879194631</c:v>
+                  <c:v>1.379310344827586</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.6711409395973155</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.369127516778524</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.342281879194631</c:v>
+                  <c:v>5.517241379310345</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -506,43 +506,43 @@
                   <c:v>Head On</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Rear End</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Overturning</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>Pedalcycles</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Right Turn</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Overturning</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Other Non-Collision</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Left Turn</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Other Non-Collision</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Pedalcycles</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Rear End</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Right Turn</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Unknown</c:v>
@@ -557,55 +557,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>26.83193583667518</c:v>
+                  <c:v>25.64874012786762</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.72329566168429</c:v>
+                  <c:v>13.31327566754419</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.296755377324098</c:v>
+                  <c:v>2.275291462955999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18.10061975938753</c:v>
+                  <c:v>7.897705904475366</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.604083120670798</c:v>
+                  <c:v>14.72358029334336</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.254830477579293</c:v>
+                  <c:v>18.1271154569387</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.4192489974480496</c:v>
+                  <c:v>0.5077096652877021</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.356543930003646</c:v>
+                  <c:v>0.2068446784505453</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.668975574188844</c:v>
+                  <c:v>0.0188040616773223</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3463361283266497</c:v>
+                  <c:v>1.823993982700263</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.984323733138899</c:v>
+                  <c:v>1.617149304249718</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2369668246445498</c:v>
+                  <c:v>2.425723956374577</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.606635071090047</c:v>
+                  <c:v>0.3196690485144791</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14.36383521691578</c:v>
+                  <c:v>1.071831515607371</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.786365293474298</c:v>
+                  <c:v>5.584806318164723</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01822821728034998</c:v>
+                  <c:v>4.099285445656261</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.4010207801676995</c:v>
+                  <c:v>0.3384731101918014</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1061,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>39.39393939393939</v>
+        <v>34.48275862068966</v>
       </c>
       <c r="C2" s="2">
-        <v>42.95302013422819</v>
+        <v>39.31034482758621</v>
       </c>
       <c r="D2" s="2">
-        <v>26.83193583667518</v>
+        <v>25.64874012786762</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>24.24242424242424</v>
+        <v>27.58620689655172</v>
       </c>
       <c r="C3" s="2">
-        <v>18.12080536912752</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2">
-        <v>12.72329566168429</v>
+        <v>13.31327566754419</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>24.24242424242424</v>
+        <v>24.13793103448276</v>
       </c>
       <c r="C4" s="2">
-        <v>6.711409395973154</v>
+        <v>4.137931034482759</v>
       </c>
       <c r="D4" s="2">
-        <v>2.296755377324098</v>
+        <v>2.275291462955999</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1103,13 +1103,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>3.03030303030303</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="C5" s="2">
-        <v>4.697986577181208</v>
+        <v>5.517241379310345</v>
       </c>
       <c r="D5" s="2">
-        <v>18.10061975938753</v>
+        <v>7.897705904475366</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1117,13 +1117,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>3.03030303030303</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="C6" s="2">
-        <v>6.711409395973154</v>
+        <v>5.517241379310345</v>
       </c>
       <c r="D6" s="2">
-        <v>1.604083120670798</v>
+        <v>14.72358029334336</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1131,13 +1131,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>3.03030303030303</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="C7" s="2">
-        <v>4.026845637583892</v>
+        <v>5.517241379310345</v>
       </c>
       <c r="D7" s="2">
-        <v>7.254830477579293</v>
+        <v>18.1271154569387</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1145,13 +1145,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>3.03030303030303</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="C8" s="2">
-        <v>2.684563758389262</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="D8" s="2">
-        <v>0.4192489974480496</v>
+        <v>0.5077096652877021</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1162,10 +1162,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="2">
-        <v>0</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="D9" s="2">
-        <v>4.356543930003646</v>
+        <v>0.2068446784505453</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="2">
-        <v>5.369127516778524</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2">
-        <v>5.668975574188844</v>
+        <v>0.0188040616773223</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1190,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
+        <v>1.379310344827586</v>
       </c>
       <c r="D11" s="2">
-        <v>0.3463361283266497</v>
+        <v>1.823993982700263</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1204,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>7.586206896551724</v>
       </c>
       <c r="D12" s="2">
-        <v>0.984323733138899</v>
+        <v>1.617149304249718</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <v>1.342281879194631</v>
+        <v>1.379310344827586</v>
       </c>
       <c r="D13" s="2">
-        <v>0.2369668246445498</v>
+        <v>2.425723956374577</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <v>0.6711409395973155</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2">
-        <v>2.606635071090047</v>
+        <v>0.3196690485144791</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>5.369127516778524</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2">
-        <v>14.36383521691578</v>
+        <v>1.071831515607371</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>1.342281879194631</v>
+        <v>5.517241379310345</v>
       </c>
       <c r="D16" s="2">
-        <v>1.786365293474298</v>
+        <v>5.584806318164723</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>0.01822821728034998</v>
+        <v>4.099285445656261</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>0.4010207801676995</v>
+        <v>0.3384731101918014</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Knox.xlsx
+++ b/output_data/charts/crashSeverityByType-Knox.xlsx
@@ -83,8 +83,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -141,7 +142,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -173,7 +174,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - Knox County</a:t>
+              <a:t>Crash Severity by Type of Crash, Knox County, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
